--- a/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
+++ b/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229FED3D-8DD2-4DC0-8A6B-83C95EFFA602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE68ADED-E934-40D0-A734-35E44232948F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,134 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이름_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름_002</t>
-  </si>
-  <si>
-    <t>이름_003</t>
-  </si>
-  <si>
-    <t>이름_004</t>
-  </si>
-  <si>
-    <t>이름_005</t>
-  </si>
-  <si>
-    <t>이름_006</t>
-  </si>
-  <si>
-    <t>이름_007</t>
-  </si>
-  <si>
-    <t>이름_008</t>
-  </si>
-  <si>
-    <t>이름_009</t>
-  </si>
-  <si>
-    <t>이름_010</t>
-  </si>
-  <si>
-    <t>이름_011</t>
-  </si>
-  <si>
-    <t>이름_012</t>
-  </si>
-  <si>
-    <t>이름_013</t>
-  </si>
-  <si>
-    <t>이름_014</t>
-  </si>
-  <si>
-    <t>이름_015</t>
-  </si>
-  <si>
-    <t>이름_016</t>
-  </si>
-  <si>
-    <t>이름_017</t>
-  </si>
-  <si>
-    <t>이름_018</t>
-  </si>
-  <si>
-    <t>이름_019</t>
-  </si>
-  <si>
-    <t>이름_020</t>
-  </si>
-  <si>
-    <t>이름_021</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 002</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 003</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 004</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 005</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 006</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 007</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 008</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 009</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 010</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 011</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 012</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 013</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 014</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 015</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 016</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 017</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 018</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 019</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 020</t>
-  </si>
-  <si>
-    <t>다이얼로그 테스트 다이얼로그 테스트 다이얼로그 테스트 021</t>
-  </si>
-  <si>
     <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -194,35 +66,119 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Character/00001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character/00002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BackGround/00001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Text_001_Scene</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BackGround/00002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BackGround/00003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BackGround/00004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Character/00020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(지지직거리는 소리와 함께 무전기에서 목소리가 들린다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…들리세요?....거기 누구 없어요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">여보세요? </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어라.. 이상하네 분명 고장나서 작동하지 않았는데..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무전기는 아직 고장나지 않았어요. 정상작동 할거에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>….차차 설명드리겠습니다. 거기서 나가고 싶으시죠?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제가 도와드리겠습니다. 다만 제게 협력해주셔야만 합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">알겠어요.. 제가 뭘 하면 되죠? </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무전기를 들고 다음방으로 가시면 됩니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아마 키패드에 다가가서. F를 누르시고 0000을 누르시면 열릴겁니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 알겠어요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(두 플레이어의 무전기가 동기화 되었습니다! V키를 눌러 대화 할 수 있습니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/00010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/00013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아하.. 근데 혹시 누구시죠??  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저는 당신이 갇혀있는 방을 조사하러 온 사람입니다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…. 예? 조사하러 오신거면 지금 제 근처에 계신거 아닌가요?? 그냥 꺼내주시면..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐라고 적혀져 있네.. "키패드의 비밀번호는 ….으로 초기화 시켜놓았다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">글씨가 지저분해서  알 수가 없어.. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/00025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임 패러독스… 블랙홀과 화이트홀.. 알 수 없는 실험 일지들 뿐이다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무전기인데.. 작동하진 않을 것 같다...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임 패러독스… 블랙홀과 화이트홀.. 지금도 꾸준히 나오는 토론주제네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키패드의 비밀번호는… 0000로 초기화 되어있다… 라고 적혀있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -590,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>5</v>
@@ -599,10 +555,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -610,19 +566,17 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -634,7 +588,7 @@
         <v>-100</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -642,19 +596,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -666,7 +618,7 @@
         <v>-100</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -674,19 +626,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -698,7 +650,7 @@
         <v>-100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -706,19 +658,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -730,7 +682,7 @@
         <v>-100</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -738,19 +690,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -762,7 +714,7 @@
         <v>-100</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -770,19 +722,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -794,7 +746,7 @@
         <v>-100</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -802,19 +754,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -826,7 +778,7 @@
         <v>-100</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -834,19 +786,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -858,7 +810,7 @@
         <v>-100</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -866,19 +818,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -890,7 +842,7 @@
         <v>-100</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -898,19 +850,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -922,7 +874,7 @@
         <v>-100</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -930,19 +882,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -954,7 +906,7 @@
         <v>-100</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -962,19 +914,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -986,7 +938,7 @@
         <v>-100</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -994,19 +946,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1018,7 +970,7 @@
         <v>-100</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1026,19 +978,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1050,7 +1002,7 @@
         <v>-100</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1058,19 +1010,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1082,7 +1034,7 @@
         <v>-100</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1090,19 +1042,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1114,7 +1066,7 @@
         <v>-100</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1125,16 +1077,16 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1146,7 +1098,7 @@
         <v>-100</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1157,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1178,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1189,16 +1141,16 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1210,7 +1162,7 @@
         <v>-100</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1218,19 +1170,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -1242,7 +1194,7 @@
         <v>-100</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -1250,19 +1202,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -1274,7 +1226,7 @@
         <v>-100</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
+++ b/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE68ADED-E934-40D0-A734-35E44232948F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED9625-B281-4379-B6A9-3D02DD84431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="42">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,6 +179,14 @@
   </si>
   <si>
     <t>키패드의 비밀번호는… 0000로 초기화 되어있다… 라고 적혀있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character/00026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>???</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -568,12 +576,14 @@
       <c r="B2" s="1">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
@@ -598,12 +608,14 @@
       <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>7</v>

--- a/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
+++ b/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED9625-B281-4379-B6A9-3D02DD84431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E960FE9A-000D-482B-8A94-9752CA10CD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="62">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,10 +66,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Text_001_Scene</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Character/00020</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -86,14 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>남주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">여보세요? </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -187,6 +175,98 @@
   </si>
   <si>
     <t>???</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혜린</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쪽지가 남겨져 있다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화분 아래에 뭐가 반짝거린다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"작은방 열쇠는 화분 아래에 숨겨놓았단다." </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화분 아래..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"선반의 비워져있는 칸의 번호는 세번째 숫자와 똑같다." </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서랍이 열린다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서랍에는 낡은 집 계약서 한장이 놓여져 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용은 알 수 없지만 1997년에 계약했다고 나와있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반쯤 찢어진 듯한 종이에 무언가가 적혀있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> “두 번째 숫자는 우리가 만났던 월인.."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐지.. 다른 반쪽도  찾아보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반쯤 찢어져 있는 듯한 종이가 소파에 껴있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건 아까 화분에서 봤었던..종이랑…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선반에는 다 책으로 가득 차있는데..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서랍에 메모가 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라고 적혀져 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//반쯤 찢어진 종이에 무언가 적혀져 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책을 놓는 선반이다. 윗칸은 법 관련 서적이 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맨 아래에는 사전들이 가득하다. 중간에는.. 아무것도 없네..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"우리가 계약한 년도의 맨 뒷자리를 비밀번호로 사용했어!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테이블에 1 = 5 라고 적혀져 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -577,13 +657,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
@@ -609,13 +689,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>7</v>
@@ -641,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>7</v>
@@ -673,13 +753,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>7</v>
@@ -705,13 +785,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>7</v>
@@ -737,13 +817,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>7</v>
@@ -769,13 +849,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>7</v>
@@ -801,13 +881,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>7</v>
@@ -833,13 +913,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>7</v>
@@ -865,13 +945,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>7</v>
@@ -897,13 +977,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>7</v>
@@ -929,13 +1009,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>7</v>
@@ -961,13 +1041,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>7</v>
@@ -993,13 +1073,13 @@
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>7</v>
@@ -1025,10 +1105,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>7</v>
@@ -1057,13 +1137,13 @@
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>7</v>
@@ -1089,13 +1169,13 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>7</v>
@@ -1121,13 +1201,13 @@
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>7</v>
@@ -1139,7 +1219,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="1">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>7</v>
@@ -1153,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>7</v>
@@ -1185,13 +1265,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>7</v>
@@ -1217,28 +1297,972 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>21</v>
+      </c>
+      <c r="I22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="1">
-        <v>-100</v>
-      </c>
-      <c r="J22" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>22</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>23</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>24</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>25</v>
+      </c>
+      <c r="I26" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>26</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>27</v>
+      </c>
+      <c r="I28" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>28</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>29</v>
+      </c>
+      <c r="I30" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>30</v>
+      </c>
+      <c r="I31" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>31</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>32</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>33</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>34</v>
+      </c>
+      <c r="I35" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>35</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>36</v>
+      </c>
+      <c r="I37" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>37</v>
+      </c>
+      <c r="I38" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>38</v>
+      </c>
+      <c r="I39" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>39</v>
+      </c>
+      <c r="I40" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>40</v>
+      </c>
+      <c r="I41" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>41</v>
+      </c>
+      <c r="I42" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>42</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>43</v>
+      </c>
+      <c r="I44" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>44</v>
+      </c>
+      <c r="I45" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>45</v>
+      </c>
+      <c r="I46" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>46</v>
+      </c>
+      <c r="I47" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>47</v>
+      </c>
+      <c r="I48" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>48</v>
+      </c>
+      <c r="I49" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>49</v>
+      </c>
+      <c r="I50" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>50</v>
+      </c>
+      <c r="I51" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>51</v>
+      </c>
+      <c r="I52" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>52</v>
+      </c>
+      <c r="I53" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>53</v>
+      </c>
+      <c r="I54" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>54</v>
+      </c>
+      <c r="I55" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>55</v>
+      </c>
+      <c r="I56" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>56</v>
+      </c>
+      <c r="I57" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>57</v>
+      </c>
+      <c r="I58" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>58</v>
+      </c>
+      <c r="I59" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
+++ b/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E960FE9A-000D-482B-8A94-9752CA10CD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD2E1F-1AA1-4FE8-BF34-B9F2A52DE948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="80">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -266,7 +266,79 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>테이블에 1 = 5 라고 적혀져 있다.</t>
+    <t xml:space="preserve">역시 여기서는 작동하지 않는건가.. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무것도 적혀있지 않은 노트다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 뒤에 문이 있는 것 같은데?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이걸 밀면 문을 열 수 있을 것 같다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔가 중요한 단서 같다.. 다만 잉크에 번져있어서 볼 수 가 없어..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">잉크가 마르면 그래도 어느정도는 볼 수 있을텐데.. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔가 적혀져있는데.. 공식인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대한 옷장이다. 왜 이런 곳에 옷장이 있는거지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1990년… 농구 경기 관련된 기록부다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1992년.. 야구 경기 관련된 기록부다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1996년.. 양궁 경기 관련된 기록부다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1988년.. 축구경기 관련된 기록부다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030년 우리나라 사격 경기 관련된 기록부인 것 같다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2033년 우리나라 태권도 경기 관련된 기록부인 것 같다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037년 우리나라 펜싱 경기 관련된 기록부인 것 같다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2040년 우리나라 골프 경기 관련된 기록부인 것 같다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잉크가 오른쪽에만 묻어서 알아볼 수가 없다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔가 잉크가.. 왼족에 부분적으로 묻었는데.. 무슨 뜻인거지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잉크가 말라서 희미하지만 내용이 보인다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -316,13 +388,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -1997,6 +2072,21 @@
       <c r="A44" s="1">
         <v>42</v>
       </c>
+      <c r="B44" s="3">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
@@ -2014,6 +2104,21 @@
       <c r="A45" s="1">
         <v>43</v>
       </c>
+      <c r="B45" s="1">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
@@ -2031,6 +2136,21 @@
       <c r="A46" s="1">
         <v>44</v>
       </c>
+      <c r="B46" s="1">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
@@ -2048,6 +2168,21 @@
       <c r="A47" s="1">
         <v>45</v>
       </c>
+      <c r="B47" s="1">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
@@ -2065,6 +2200,21 @@
       <c r="A48" s="1">
         <v>46</v>
       </c>
+      <c r="B48" s="1">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
@@ -2082,6 +2232,21 @@
       <c r="A49" s="1">
         <v>47</v>
       </c>
+      <c r="B49" s="1">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
@@ -2098,6 +2263,21 @@
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -2116,6 +2296,21 @@
       <c r="A51" s="1">
         <v>49</v>
       </c>
+      <c r="B51" s="1">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
@@ -2133,6 +2328,21 @@
       <c r="A52" s="1">
         <v>50</v>
       </c>
+      <c r="B52" s="1">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
@@ -2150,6 +2360,21 @@
       <c r="A53" s="1">
         <v>51</v>
       </c>
+      <c r="B53" s="1">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
@@ -2167,6 +2392,21 @@
       <c r="A54" s="1">
         <v>52</v>
       </c>
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
@@ -2184,6 +2424,21 @@
       <c r="A55" s="1">
         <v>53</v>
       </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
@@ -2201,6 +2456,21 @@
       <c r="A56" s="1">
         <v>54</v>
       </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G56" s="1">
         <v>0</v>
       </c>
@@ -2218,6 +2488,21 @@
       <c r="A57" s="1">
         <v>55</v>
       </c>
+      <c r="B57" s="1">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
@@ -2235,6 +2520,21 @@
       <c r="A58" s="1">
         <v>56</v>
       </c>
+      <c r="B58" s="1">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
@@ -2252,6 +2552,21 @@
       <c r="A59" s="1">
         <v>57</v>
       </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
@@ -2262,6 +2577,157 @@
         <v>-100</v>
       </c>
       <c r="J59" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>59</v>
+      </c>
+      <c r="I60" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>60</v>
+      </c>
+      <c r="I61" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>61</v>
+      </c>
+      <c r="I62" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" s="1">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>62</v>
+      </c>
+      <c r="I63" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>63</v>
+      </c>
+      <c r="I64" s="1">
+        <v>-100</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
+++ b/ChronoLInk/Assets/Resources/ExcelDB/DialogueDB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD2E1F-1AA1-4FE8-BF34-B9F2A52DE948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08040297-F077-40DF-A6A1-974C13071291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,10 +198,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">"선반의 비워져있는 칸의 번호는 세번째 숫자와 똑같다." </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>서랍이 열린다!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -234,10 +230,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이건 아까 화분에서 봤었던..종이랑…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>선반에는 다 책으로 가득 차있는데..?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -339,6 +331,14 @@
   </si>
   <si>
     <t>잉크가 말라서 희미하지만 내용이 보인다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"선반의 비워져있는 칸의 번호는 세번째 숫자와 똑같다." 라고 적혀있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용은 "따듯한 6월.." 이건 아까 화분에서 봤었던..종이랑…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -860,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
@@ -924,7 +924,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -988,7 +988,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>18</v>
@@ -1020,7 +1020,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>19</v>
@@ -1084,7 +1084,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>21</v>
@@ -1116,7 +1116,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>22</v>
@@ -1340,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>35</v>
@@ -1372,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>36</v>
@@ -1535,7 +1535,7 @@
         <v>39</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>25</v>
@@ -1567,7 +1567,7 @@
         <v>39</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>25</v>
@@ -1599,7 +1599,7 @@
         <v>39</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>25</v>
@@ -1631,7 +1631,7 @@
         <v>39</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>25</v>
@@ -1663,7 +1663,7 @@
         <v>39</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>25</v>
@@ -1695,7 +1695,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>25</v>
@@ -1724,10 +1724,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>11</v>
@@ -1756,10 +1756,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>11</v>
@@ -1788,10 +1788,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>11</v>
@@ -1820,10 +1820,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>11</v>
@@ -1852,10 +1852,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>11</v>
@@ -1884,10 +1884,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>11</v>
@@ -1916,10 +1916,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>11</v>
@@ -1948,10 +1948,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>11</v>
@@ -1980,10 +1980,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>11</v>
@@ -2012,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>11</v>
@@ -2044,10 +2044,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>11</v>
@@ -2079,7 +2079,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>25</v>
@@ -2111,7 +2111,7 @@
         <v>39</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>25</v>
@@ -2143,7 +2143,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>25</v>
@@ -2175,7 +2175,7 @@
         <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>25</v>
@@ -2207,7 +2207,7 @@
         <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>25</v>
@@ -2239,7 +2239,7 @@
         <v>39</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>25</v>
@@ -2271,7 +2271,7 @@
         <v>39</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>25</v>
@@ -2303,7 +2303,7 @@
         <v>39</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>25</v>
@@ -2335,7 +2335,7 @@
         <v>39</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>25</v>
@@ -2367,7 +2367,7 @@
         <v>39</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>25</v>
@@ -2396,10 +2396,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>11</v>
@@ -2428,10 +2428,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>11</v>
@@ -2460,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>11</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>11</v>
@@ -2524,10 +2524,10 @@
         <v>1</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>11</v>
@@ -2556,10 +2556,10 @@
         <v>1</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>11</v>
@@ -2588,10 +2588,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>11</v>
@@ -2620,10 +2620,10 @@
         <v>1</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>11</v>
@@ -2652,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>11</v>
@@ -2681,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>11</v>
@@ -2710,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>11</v>
